--- a/daily_matches/job_matches_2026-03-29.xlsx
+++ b/daily_matches/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI &amp; Data Solution Architect</t>
+          <t>Data Validation Engineer (ML)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.3</v>
+        <v>35.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, S3, Glue</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e27010d95a9e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0aa9d1342b93a57e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,28 +517,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Hugging Face, TensorFlow, PyTorch, OpenCV, AWS SageMaker, MLflow, FastAPI</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a04359062554215</t>
+          <t>https://www.indeed.com/viewjob?jk=53dc0c790b0e9f01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior GCP ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Cortex, EC2, Redshift, FastAPI, Docker, CI/CD, Jenkins</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=57ac54fc6dbaa07d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Generative AI Operations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hugging Face, TensorFlow, PyTorch, OpenCV, AWS SageMaker, MLflow, FastAPI, Docker</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Git, Databricks, Matplotlib</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
+          <t>https://www.indeed.com/viewjob?jk=256ad3780d608a63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c11cfcc9f1bf30</t>
+          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c550c77ccceab6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,28 +692,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, EC2, Docker</t>
+          <t>AI Engineer, TensorFlow, PyTorch, S3, EC2, Glue, Docker, Apache Airflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9d26ddb2926164</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Generative AI Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,67 +723,67 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, EC2, Docker</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19619fd982cb226b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1a8d6032d91a3b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Git, Databricks, Matplotlib</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Cassandra, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda18e1edc32d907</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Pinecone, S3, FastAPI, Docker, CI/CD, Jenkins, Git</t>
+          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
+          <t>https://www.indeed.com/viewjob?jk=06c2d442119e17ab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Generative AI Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, AWS SageMaker, Docker</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, AWS SageMaker, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff2d0b54b76e751</t>
+          <t>https://www.indeed.com/viewjob?jk=1b869b897d01a078</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Senior GCP ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3758399121f8ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Cloud Connectivity Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,67 +898,67 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, AWS SageMaker, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6209149dbce5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c77225b5317f7fa5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Hadoop</t>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,32 +968,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Kafka</t>
+          <t>AI Engineer, LangChain, TensorFlow, PyTorch, XGBoost, LightGBM, spaCy, NLTK, Kafka, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
+          <t>https://www.indeed.com/viewjob?jk=171d10db3743d0f0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>Generative AI Operations Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=690091240de9b38e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>RAG, Azure ML, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeea247b3aca2004</t>
+          <t>https://www.indeed.com/viewjob?jk=3d2fcaa9fabe444f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop, Python, SQL, R</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, FAISS, Pinecone, MLflow, Docker, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,77 +1126,77 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76017c66feb672d</t>
+          <t>https://www.indeed.com/viewjob?jk=da1d596520cc8b24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Internship - Applied AI Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Infineon Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Data Lake, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea1cfdbac35133f</t>
+          <t>https://www.indeed.com/viewjob?jk=7cb5348c48791ea3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Internship - Applied AI Engineer</t>
+          <t>Streaming ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infineon Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Data Lake, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd19e08e976a22d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9cdc8511297a4b3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>TensorFlow, PyTorch, Data Lake, FastAPI, CI/CD, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd067cf97902d7</t>
+          <t>https://www.indeed.com/viewjob?jk=690b8c362e819694</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Data Validation Engineer (ML)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,32 +1248,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e0ae02f91497ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=edc0d093f962a83d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,32 +1283,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307f4c591db97d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba7b22fdc610387</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,32 +1318,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>LangChain, Hugging Face, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b72773b56542af0</t>
+          <t>https://www.indeed.com/viewjob?jk=20645641087dae67</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,375 +1353,60 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
+          <t>Data Lake, Docker, CI/CD, Jenkins, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a6bb2fde4c7bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Investment Risk &amp; Analytics - Quant Modeling Senior Associate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grove Safety</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, EC2, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3436a90ba214b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CrowdStrike AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Data Lake, FastAPI, CI/CD, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ee705463351f07</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CrowdStrike AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e5b05382a3df66</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CrowdStrike AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ccfa0ab3bb5242</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior AI Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Dataflow, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb59e700c800a30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - Medical Device Industry</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Berwyn, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Docker, Jenkins, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f966a8b56b5b8ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba279ca011de8fe8</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SAP AI Business Services Consultant</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd0072e7e2246ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Generative AI Operations Expert</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf90fab95ef508c</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Platform/MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Bright Machines</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ce8d4aeffea56c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2102bca689daf18</t>
         </is>
       </c>
     </row>
